--- a/results/job_matches_2026-10-17.xlsx
+++ b/results/job_matches_2026-10-17.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,59 +554,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed61fbb4cf30f4</t>
+          <t>https://www.indeed.com/viewjob?jk=618da1fd3349a9e4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Builders</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618da1fd3349a9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea8c47e2b4c9527</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AID&amp;E - AI Governance &amp; Responsible AI - Senior - Consulting</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Vertex AI, Scala, Oracle, Power BI, MLOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,24 +624,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7623ac8c1f35092b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1b0e4f8d04d392</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AID&amp;E - AI Governance &amp; Responsible AI - Senior - Consulting</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Vertex AI, Scala, Oracle, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1b0e4f8d04d392</t>
+          <t>https://www.indeed.com/viewjob?jk=7623ac8c1f35092b</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Erlanger, KY, USA USA</t>
+          <t>Cincinnati, OH, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0631f7e796ccb99</t>
+          <t>https://www.indeed.com/viewjob?jk=71b643cc943fe0db</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Clinical AI/Data Science Eng I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northridge, CA, USA USA</t>
+          <t>Arlington, TX, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,24 +939,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af3590cefd76d17</t>
+          <t>https://www.indeed.com/viewjob?jk=e76753920938549c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Clinical AI/Data Science Eng I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, USA USA</t>
+          <t>Northridge, CA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
+          <t>https://www.indeed.com/viewjob?jk=4af3590cefd76d17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sunrise, FL, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
+          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solution Architect, AI &amp; Cloud</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Advantage Investigations</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NC, USA USA</t>
+          <t>Highlands Ranch, CO, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
+          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Solution Architect, AI &amp; Cloud</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Advantage Investigations</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>NC, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54fb94ffc70f02c</t>
+          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c54fb94ffc70f02c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Data analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T and T Consulting Services, Inc</t>
+          <t>SEGULA Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Falmouth, MA, USA USA</t>
+          <t>Auburn Hills, MI, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
+          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
         </is>
       </c>
     </row>
@@ -1196,187 +1196,187 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Grady Health System</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Application Engineer - AI</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Allspring Global Investments Holdings, LLC</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
+          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Platform</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>T and T Consulting Services, Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Omaha, NE, USA USA</t>
+          <t>Falmouth, MA, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Databricks Lakehouse, SQL Server, MongoDB, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e10df7e2a6a34c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New Orleans, LA, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d8ff32333b0bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Application Engineer - AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Allspring Global Investments Holdings, LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IL, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64ebc7fe9e07abe</t>
+          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA USA</t>
+          <t>Omaha, NE, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Databricks Lakehouse, SQL Server, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747a30b2ad95b161</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e10df7e2a6a34c</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>New Orleans, LA, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1429,24 +1429,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc303d21d5766b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d8ff32333b0bbf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mid-Level Full Stack Developer</t>
+          <t>Senior Cloud Services Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Academian</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>KY, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,34 +1454,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f47628601624696</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT-Engineer</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Clifton Park, NY, USA USA</t>
+          <t>IL, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca652d2e35ef7a6</t>
+          <t>https://www.indeed.com/viewjob?jk=f64ebc7fe9e07abe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Security Engineer - Network Edge Security</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, USA USA</t>
+          <t>Hartford, CT, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,34 +1524,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42cd7af563ba184</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Solution Engineer (Expansion)</t>
+          <t>Mid-Level Full Stack Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Academian</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e9257f6a31076a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f47628601624696</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>IT-Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Clifton Park, NY, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e8eea54405bd1d</t>
+          <t>https://www.indeed.com/viewjob?jk=aca652d2e35ef7a6</t>
         </is>
       </c>
     </row>
@@ -1716,17 +1716,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Platform Engineer - ClickHouse</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Qualys</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Foster City, CA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,24 +1744,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
+          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,34 +1769,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fandom</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Virginia Beach, VA, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,14 +1814,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
+          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, Databricks, ETL</t>
+          <t>Software Engineering III - AWS, GCP, Terraform</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Software Engineer II - Python, Databricks, ETL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,24 +1884,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
+          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,24 +1919,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LakeFusion</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,24 +1954,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71bf44c1b8f903d7</t>
+          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Enterprise Account Executive (Telco)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bellevue, WA, USA USA</t>
+          <t>MS, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,34 +1979,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65e1984b6c60dff9</t>
+          <t>https://www.indeed.com/viewjob?jk=37dcd8fafdae37ab</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Amalgamated Bank</t>
+          <t>LakeFusion</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,24 +2024,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
+          <t>https://www.indeed.com/viewjob?jk=71bf44c1b8f903d7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Enterprise Account Executive</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New Orleans, LA, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,34 +2049,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1fd87eba80653d8</t>
+          <t>https://www.indeed.com/viewjob?jk=65e1984b6c60dff9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Sr. Software Engineer, MarTech (Remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New Orleans, LA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c8f5cd15d15d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. AISecOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Amalgamated Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,34 +2119,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
+          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cyber Security Cloud Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>National Carwash Solutions, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Detroit, MI, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,85 +2154,295 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
+          <t>https://www.indeed.com/viewjob?jk=93631fa5e9e6f5fb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DBT / Analytical Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>InApp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Detroit, MI, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Snowflake, Oracle, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, Fact Tables, ELT, dbt, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7b553b68d58c93</t>
+          <t>https://www.indeed.com/viewjob?jk=c769b23903df4a93</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>AI Engineer III</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, USA USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1fd87eba80653d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sr. AISecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ally Financial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, USA USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Cyber Security Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>National Carwash Solutions, Inc.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, USA USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Engineer- Software, AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>American Honda Motor</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>East Liberty, OH, USA USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DBT / Analytical Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>InApp</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Snowflake, Oracle, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, Fact Tables, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc7b553b68d58c93</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Infrastructure</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>OneMain Financial</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>West Valley City, UT, USA USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06de8d1193912d34</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Automation &amp; Analytics Engineer</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>KPIT Technologies</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D58" t="n">
         <v>10.4</v>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=34953ee9e43bedae</t>
         </is>

--- a/results/job_matches_2026-10-17.xlsx
+++ b/results/job_matches_2026-10-17.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,17 +491,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 4, Real-time Data Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lowenstein Sandler</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Roseland, NJ, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -509,42 +509,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a132c337eb72501b</t>
+          <t>https://www.indeed.com/viewjob?jk=84b8331b9f96dda9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lowenstein Sandler</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Roseland, NJ, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,59 +554,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618da1fd3349a9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a132c337eb72501b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Builders</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea8c47e2b4c9527</t>
+          <t>https://www.indeed.com/viewjob?jk=618da1fd3349a9e4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>Builders</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,34 +614,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1b0e4f8d04d392</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea8c47e2b4c9527</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AID&amp;E - AI Governance &amp; Responsible AI - Senior - Consulting</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Vertex AI, Scala, Oracle, Power BI, MLOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,24 +659,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7623ac8c1f35092b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1b0e4f8d04d392</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>AID&amp;E - AI Governance &amp; Responsible AI - Senior - Consulting</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Antonio, TX, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Vertex AI, Scala, Oracle, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da49be1f8af5184</t>
+          <t>https://www.indeed.com/viewjob?jk=7623ac8c1f35092b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prolaio</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e6c438a9913e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=3da49be1f8af5184</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Prolaio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Edison, NJ, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257cf3b26e3ac665</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e6c438a9913e4f</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>Edison, NJ, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3abc7d40fac1d76</t>
+          <t>https://www.indeed.com/viewjob?jk=257cf3b26e3ac665</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington, TX, USA USA</t>
+          <t>Miami, FL, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b2991361adabe1</t>
+          <t>https://www.indeed.com/viewjob?jk=a3abc7d40fac1d76</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, USA USA</t>
+          <t>Arlington, TX, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b643cc943fe0db</t>
+          <t>https://www.indeed.com/viewjob?jk=84b2991361adabe1</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington, TX, USA USA</t>
+          <t>Cincinnati, OH, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e76753920938549c</t>
+          <t>https://www.indeed.com/viewjob?jk=71b643cc943fe0db</t>
         </is>
       </c>
     </row>
@@ -1016,25 +1016,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sunrise, FL, USA USA</t>
+          <t>Erlanger, KY, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0631f7e796ccb99</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solution Architect, AI &amp; Cloud</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Advantage Investigations</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NC, USA USA</t>
+          <t>Highlands Ranch, CO, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
+          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Solution Architect, AI &amp; Cloud</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Advantage Investigations</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>NC, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,59 +1149,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54fb94ffc70f02c</t>
+          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data analyst/Data Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SEGULA Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
+          <t>https://www.indeed.com/viewjob?jk=c54fb94ffc70f02c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Grady Health System</t>
+          <t>SEGULA Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Auburn Hills, MI, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
+          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Grady Health System</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,34 +1244,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T and T Consulting Services, Inc</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Falmouth, MA, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,69 +1279,69 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
+          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>T and T Consulting Services, Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Falmouth, MA, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Application Engineer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Allspring Global Investments Holdings, LLC</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,52 +1349,52 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Platform</t>
+          <t>Application Engineer - AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>Allspring Global Investments Holdings, LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Omaha, NE, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Databricks Lakehouse, SQL Server, MongoDB, Data Modeling</t>
+          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e10df7e2a6a34c</t>
+          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New Orleans, LA, USA USA</t>
+          <t>Detroit, MI, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1429,24 +1429,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d8ff32333b0bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=4ec30982bb4277ab</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Services Engineer</t>
+          <t>Senior Data Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KY, USA USA</t>
+          <t>Omaha, NE, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,34 +1454,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Databricks Lakehouse, SQL Server, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e10df7e2a6a34c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Sr Engineer, ML, SMAI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IL, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,34 +1489,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64ebc7fe9e07abe</t>
+          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Cloud Services Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hartford, CT, USA USA</t>
+          <t>KY, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,24 +1534,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mid-Level Full Stack Developer</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Academian</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>IL, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f47628601624696</t>
+          <t>https://www.indeed.com/viewjob?jk=f64ebc7fe9e07abe</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IT-Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Clifton Park, NY, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,34 +1594,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca652d2e35ef7a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc303d21d5766b4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Patterson Companies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CA, USA USA</t>
+          <t>Hartford, CT, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,42 +1629,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f903c2e0d09915</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mid-Level Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Academian</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,32 +1674,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13eef95390e13e6</t>
+          <t>https://www.indeed.com/viewjob?jk=6f47628601624696</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Customer Engineer, Data &amp; Analytics</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Premier Cloud</t>
+          <t>Patterson Companies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>CA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
+          <t>https://www.indeed.com/viewjob?jk=52f903c2e0d09915</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - ClickHouse</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Qualys</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Foster City, CA, USA USA</t>
+          <t>Anaheim, CA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,24 +1744,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
+          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,34 +1769,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
+          <t>https://www.indeed.com/viewjob?jk=a13eef95390e13e6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Customer Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Redshift, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,24 +1814,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
+          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
+          <t>Senior Platform Engineer - ClickHouse</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Qualys</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Foster City, CA, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,34 +1839,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
+          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, Databricks, ETL</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,34 +1874,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Fandom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Virginia Beach, VA, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,24 +1919,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
+          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineering III - AWS, GCP, Terraform</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,24 +1954,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer II - Python, Databricks, ETL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MS, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,34 +1979,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dcd8fafdae37ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LakeFusion</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,24 +2024,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71bf44c1b8f903d7</t>
+          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enterprise Account Executive</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bellevue, WA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65e1984b6c60dff9</t>
+          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, MarTech (Remote)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>MS, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
+          <t>https://www.indeed.com/viewjob?jk=37dcd8fafdae37ab</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amalgamated Bank</t>
+          <t>LakeFusion</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
+          <t>https://www.indeed.com/viewjob?jk=71bf44c1b8f903d7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Sr. Software Engineer, MarTech (Remote)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Detroit, MI, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93631fa5e9e6f5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Amalgamated Bank</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Detroit, MI, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c769b23903df4a93</t>
+          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
         </is>
       </c>
     </row>
@@ -2241,17 +2241,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. AISecOps Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
+          <t>https://www.indeed.com/viewjob?jk=feed41e065eee097</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cyber Security Cloud Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>National Carwash Solutions, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2294,42 +2294,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
+          <t>https://www.indeed.com/viewjob?jk=38b6d459902ead32</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineer- Software, AI and Data Analytics</t>
+          <t>Sr. AISecOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Honda Motor</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>East Liberty, OH, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,32 +2339,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DBT / Analytical Engineer</t>
+          <t>Cyber Security Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>InApp</t>
+          <t>National Carwash Solutions, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Snowflake, Oracle, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, Fact Tables, ELT, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7b553b68d58c93</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer - Infrastructure</t>
+          <t>Engineer- Software, AI and Data Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>American Honda Motor</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>West Valley City, UT, USA USA</t>
+          <t>East Liberty, OH, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06de8d1193912d34</t>
+          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Automation &amp; Analytics Engineer</t>
+          <t>DBT / Analytical Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>InApp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sunrise, FL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,15 +2434,120 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>Snowflake, Oracle, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, Fact Tables, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc7b553b68d58c93</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Vibhutechinc</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Infrastructure</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>OneMain Financial</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>West Valley City, UT, USA USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06de8d1193912d34</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Automation &amp; Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>KPIT Technologies</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=34953ee9e43bedae</t>
         </is>

--- a/results/job_matches_2026-10-17.xlsx
+++ b/results/job_matches_2026-10-17.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,52 +561,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Builders</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618da1fd3349a9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea8c47e2b4c9527</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AID&amp;E - AI Governance &amp; Responsible AI - Senior - Consulting</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Builders</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,17 +614,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Vertex AI, Scala, Oracle, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea8c47e2b4c9527</t>
+          <t>https://www.indeed.com/viewjob?jk=7623ac8c1f35092b</t>
         </is>
       </c>
     </row>
@@ -666,25 +666,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AID&amp;E - AI Governance &amp; Responsible AI - Senior - Consulting</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Prolaio</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Vertex AI, Scala, Oracle, Power BI, MLOps</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7623ac8c1f35092b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e6c438a9913e4f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>New Hampshire Mutual Bancorp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Antonio, TX, USA USA</t>
+          <t>Concord, NH, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da49be1f8af5184</t>
+          <t>https://www.indeed.com/viewjob?jk=013237d4696c82bd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prolaio</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Erlanger, KY, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e6c438a9913e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0631f7e796ccb99</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New Hampshire Mutual Bancorp</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Concord, NH, USA USA</t>
+          <t>Arlington, TX, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,24 +799,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013237d4696c82bd</t>
+          <t>https://www.indeed.com/viewjob?jk=84b2991361adabe1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Clinical AI/Data Science Eng I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Edison, NJ, USA USA</t>
+          <t>Northridge, CA, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257cf3b26e3ac665</t>
+          <t>https://www.indeed.com/viewjob?jk=4af3590cefd76d17</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arlington, TX, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b2991361adabe1</t>
+          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b643cc943fe0db</t>
+          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Clinical AI/Data Science Eng I</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northridge, CA, USA USA</t>
+          <t>Highlands Ranch, CO, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af3590cefd76d17</t>
+          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Solution Architect, AI &amp; Cloud</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Advantage Investigations</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, USA USA</t>
+          <t>NC, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
+          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Erlanger, KY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,102 +1044,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0631f7e796ccb99</t>
+          <t>https://www.indeed.com/viewjob?jk=c54fb94ffc70f02c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
+          <t>Data analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>SEGULA Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sunrise, FL, USA USA</t>
+          <t>Auburn Hills, MI, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
+          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Grady Health System</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solution Architect, AI &amp; Cloud</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Advantage Investigations</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NC, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,102 +1149,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
+          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>T and T Consulting Services, Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Falmouth, MA, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54fb94ffc70f02c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data analyst/Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SEGULA Technologies</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
+          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Engineer - AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Grady Health System</t>
+          <t>Allspring Global Investments Holdings, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,137 +1254,137 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
+          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Detroit, MI, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ec30982bb4277ab</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Senior Data Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>T and T Consulting Services, Inc</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Falmouth, MA, USA USA</t>
+          <t>Omaha, NE, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Databricks Lakehouse, SQL Server, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e10df7e2a6a34c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Engineer, ML, SMAI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Application Engineer - AI</t>
+          <t>Senior Cloud Services Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Allspring Global Investments Holdings, LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>KY, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Detroit, MI, USA USA</t>
+          <t>IL, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,34 +1419,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ec30982bb4277ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f64ebc7fe9e07abe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Platform</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Omaha, NE, USA USA</t>
+          <t>Hartford, CT, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,34 +1454,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Databricks Lakehouse, SQL Server, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e10df7e2a6a34c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Engineer, ML, SMAI</t>
+          <t>Mid-Level Full Stack Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Academian</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boise, ID, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,34 +1489,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
+          <t>https://www.indeed.com/viewjob?jk=6f47628601624696</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Services Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KY, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,24 +1534,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc303d21d5766b4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IL, USA USA</t>
+          <t>New Orleans, LA, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64ebc7fe9e07abe</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d8ff32333b0bbf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Patterson Companies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>CA, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,42 +1594,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc303d21d5766b4</t>
+          <t>https://www.indeed.com/viewjob?jk=52f903c2e0d09915</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hartford, CT, USA USA</t>
+          <t>Anaheim, CA, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,32 +1639,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mid-Level Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Academian</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,32 +1674,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f47628601624696</t>
+          <t>https://www.indeed.com/viewjob?jk=a13eef95390e13e6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Customer Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Patterson Companies</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>Redshift, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f903c2e0d09915</t>
+          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Platform Engineer - ClickHouse</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Qualys</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Anaheim, CA, USA USA</t>
+          <t>Foster City, CA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,24 +1744,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
+          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,34 +1769,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13eef95390e13e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Customer Engineer, Data &amp; Analytics</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Premier Cloud</t>
+          <t>Fandom</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Virginia Beach, VA, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,24 +1814,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - ClickHouse</t>
+          <t>Software Engineering III - AWS, GCP, Terraform</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Qualys</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Foster City, CA, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,34 +1839,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer II - Python, Databricks, ETL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,34 +1874,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
+          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,24 +1919,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
+          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,24 +1954,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
+          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, Databricks, ETL</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>MS, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,34 +1979,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
+          <t>https://www.indeed.com/viewjob?jk=37dcd8fafdae37ab</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>LakeFusion</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,24 +2024,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
+          <t>https://www.indeed.com/viewjob?jk=71bf44c1b8f903d7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. Software Engineer, MarTech (Remote)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,34 +2049,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Amalgamated Bank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MS, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,34 +2084,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dcd8fafdae37ab</t>
+          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LakeFusion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>New Orleans, LA, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,34 +2119,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71bf44c1b8f903d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1fd87eba80653d8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, MarTech (Remote)</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
+          <t>https://www.indeed.com/viewjob?jk=839f9dfae4453b23</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Amalgamated Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,34 +2189,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
+          <t>https://www.indeed.com/viewjob?jk=feed41e065eee097</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Sr. AISecOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New Orleans, LA, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,24 +2234,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1fd87eba80653d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Cyber Security Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>National Carwash Solutions, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,42 +2259,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feed41e065eee097</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Engineer- Software, AI and Data Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Honda Motor</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>East Liberty, OH, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,32 +2304,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b6d459902ead32</t>
+          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. AISecOps Engineer</t>
+          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Vibhutechinc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,59 +2339,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cyber Security Cloud Engineer</t>
+          <t>Senior Engineer - Infrastructure</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>National Carwash Solutions, Inc.</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>West Valley City, UT, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
+          <t>https://www.indeed.com/viewjob?jk=06de8d1193912d34</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer- Software, AI and Data Analytics</t>
+          <t>Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Honda Motor</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>East Liberty, OH, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,155 +2399,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>DBT / Analytical Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>InApp</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Snowflake, Oracle, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, Fact Tables, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7b553b68d58c93</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Vibhutechinc</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Infrastructure</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>OneMain Financial</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>West Valley City, UT, USA USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06de8d1193912d34</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Automation &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>KPIT Technologies</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=34953ee9e43bedae</t>
         </is>

--- a/results/job_matches_2026-10-17.xlsx
+++ b/results/job_matches_2026-10-17.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,25 +561,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Builders</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Englewood, CO, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,24 +589,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea8c47e2b4c9527</t>
+          <t>https://www.indeed.com/viewjob?jk=50267e1f88400770</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AID&amp;E - AI Governance &amp; Responsible AI - Senior - Consulting</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Builders</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,34 +614,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Vertex AI, Scala, Oracle, Power BI, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7623ac8c1f35092b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea8c47e2b4c9527</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AID&amp;E - AI Governance &amp; Responsible AI - Senior - Consulting</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Vertex AI, Scala, Snowflake, PostgreSQL, MySQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Vertex AI, Scala, Oracle, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,67 +659,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1b0e4f8d04d392</t>
+          <t>https://www.indeed.com/viewjob?jk=7623ac8c1f35092b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prolaio</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Kafka</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e6c438a9913e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0648fe794d2cbb5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New Hampshire Mutual Bancorp</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Concord, NH, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013237d4696c82bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3da49be1f8af5184</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>Prolaio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Erlanger, KY, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0631f7e796ccb99</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e6c438a9913e4f</t>
         </is>
       </c>
     </row>
@@ -841,25 +841,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>Sunrise, FL, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3abc7d40fac1d76</t>
+          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, USA USA</t>
+          <t>Highlands Ranch, CO, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
+          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
+          <t>Solution Architect, AI &amp; Cloud</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Advantage Investigations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunrise, FL, USA USA</t>
+          <t>NC, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,102 +939,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
+          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Grady Health System</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solution Architect, AI &amp; Cloud</t>
+          <t>Data analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Advantage Investigations</t>
+          <t>SEGULA Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NC, USA USA</t>
+          <t>Auburn Hills, MI, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
+          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54fb94ffc70f02c</t>
+          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data analyst/Data Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SEGULA Technologies</t>
+          <t>T and T Consulting Services, Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, USA USA</t>
+          <t>Falmouth, MA, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
         </is>
       </c>
     </row>
@@ -1091,90 +1091,90 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Grady Health System</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Application Engineer - AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T and T Consulting Services, Inc</t>
+          <t>Allspring Global Investments Holdings, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Falmouth, MA, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,77 +1184,77 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
+          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Engineer, ML, SMAI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Application Engineer - AI</t>
+          <t>Senior Data Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Allspring Global Investments Holdings, LLC</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Omaha, NE, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Databricks Lakehouse, SQL Server, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e10df7e2a6a34c</t>
         </is>
       </c>
     </row>
@@ -1296,17 +1296,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Platform</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Omaha, NE, USA USA</t>
+          <t>New Orleans, LA, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,34 +1314,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Databricks Lakehouse, SQL Server, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e10df7e2a6a34c</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d8ff32333b0bbf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Engineer, ML, SMAI</t>
+          <t>Senior Cloud Services Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boise, ID, USA USA</t>
+          <t>KY, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,24 +1359,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Services Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KY, USA USA</t>
+          <t>Hartford, CT, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IL, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,34 +1419,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64ebc7fe9e07abe</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc303d21d5766b4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Patterson Companies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hartford, CT, USA USA</t>
+          <t>CA, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,77 +1454,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=52f903c2e0d09915</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mid-Level Full Stack Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Academian</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Anaheim, CA, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f47628601624696</t>
+          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Platform Engineer - ClickHouse</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Qualys</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>Foster City, CA, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,32 +1534,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc303d21d5766b4</t>
+          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Orleans, LA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,32 +1569,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d8ff32333b0bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Software Engineering III - AWS, GCP, Terraform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Patterson Companies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CA, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,24 +1604,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f903c2e0d09915</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer II - Python, Databricks, ETL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Anaheim, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,34 +1629,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
+          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,24 +1674,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13eef95390e13e6</t>
+          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Customer Engineer, Data &amp; Analytics</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Premier Cloud</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
+          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - ClickHouse</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Qualys</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Foster City, CA, USA USA</t>
+          <t>AL, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,24 +1744,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
+          <t>https://www.indeed.com/viewjob?jk=42f767cc0538bac7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>LakeFusion</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,34 +1769,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
+          <t>https://www.indeed.com/viewjob?jk=71bf44c1b8f903d7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Software Engineer, MarTech (Remote)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,34 +1804,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
+          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Amalgamated Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
+          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, Databricks, ETL</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Detroit, MI, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,34 +1874,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
+          <t>https://www.indeed.com/viewjob?jk=93631fa5e9e6f5fb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Detroit, MI, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,34 +1909,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
+          <t>https://www.indeed.com/viewjob?jk=c769b23903df4a93</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>New Orleans, LA, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,34 +1944,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=18c8f5cd15d15d9f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. AISecOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MS, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,24 +1989,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dcd8fafdae37ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Cyber Security Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LakeFusion</t>
+          <t>National Carwash Solutions, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,32 +2024,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71bf44c1b8f903d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, MarTech (Remote)</t>
+          <t>Engineer- Software, AI and Data Analytics</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>American Honda Motor</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>East Liberty, OH, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,67 +2059,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
+          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Amalgamated Bank</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
+          <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vibhutechinc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New Orleans, LA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,32 +2129,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1fd87eba80653d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Engineer - Infrastructure</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>West Valley City, UT, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,252 +2164,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839f9dfae4453b23</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=feed41e065eee097</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Sr. AISecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Ally Financial</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, USA USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Cyber Security Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>National Carwash Solutions, Inc.</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Engineer- Software, AI and Data Analytics</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>American Honda Motor</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>East Liberty, OH, USA USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Vibhutechinc</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Infrastructure</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>OneMain Financial</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>West Valley City, UT, USA USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=06de8d1193912d34</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Automation &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>KPIT Technologies</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34953ee9e43bedae</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-17.xlsx
+++ b/results/job_matches_2026-10-17.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,35 +456,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Database Engineer / Data Platform Engineer - Contract</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Techniche Software Solutions</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c608dc1a7f91a8fd</t>
+          <t>https://www.indeed.com/viewjob?jk=22dabb7901b93b25</t>
         </is>
       </c>
     </row>
@@ -526,60 +526,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lowenstein Sandler</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Roseland, NJ, USA USA</t>
+          <t>Englewood, CO, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a132c337eb72501b</t>
+          <t>https://www.indeed.com/viewjob?jk=50267e1f88400770</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Builders</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Englewood, CO, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,24 +589,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50267e1f88400770</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea8c47e2b4c9527</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Builders</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea8c47e2b4c9527</t>
+          <t>https://www.indeed.com/viewjob?jk=e0648fe794d2cbb5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AID&amp;E - AI Governance &amp; Responsible AI - Senior - Consulting</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Prolaio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Vertex AI, Scala, Oracle, Power BI, MLOps</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,67 +659,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7623ac8c1f35092b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e6c438a9913e4f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Arlington, TX, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0648fe794d2cbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=84b2991361adabe1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Clinical AI/Data Science Eng I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Antonio, TX, USA USA</t>
+          <t>Northridge, CA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da49be1f8af5184</t>
+          <t>https://www.indeed.com/viewjob?jk=4af3590cefd76d17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prolaio</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Highlands Ranch, CO, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e6c438a9913e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect, AI &amp; Cloud</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Advantage Investigations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arlington, TX, USA USA</t>
+          <t>NC, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,102 +799,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b2991361adabe1</t>
+          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Clinical AI/Data Science Eng I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Grady Health System</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Northridge, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af3590cefd76d17</t>
+          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III, Full Stack - Global Servicing Technology</t>
+          <t>Data analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>SEGULA Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunrise, FL, USA USA</t>
+          <t>Auburn Hills, MI, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf12a0beeb32108b</t>
+          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,42 +904,42 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Solution Architect, AI &amp; Cloud</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Advantage Investigations</t>
+          <t>T and T Consulting Services, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NC, USA USA</t>
+          <t>Falmouth, MA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
         </is>
       </c>
     </row>
@@ -951,55 +951,55 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grady Health System</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data analyst/Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SEGULA Technologies</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,67 +1009,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
+          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Application Engineer - AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Allspring Global Investments Holdings, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
+          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Sr Engineer, ML, SMAI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T and T Consulting Services, Inc</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Falmouth, MA, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,67 +1079,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Detroit, MI, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ec30982bb4277ab</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Cloud Services Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>FL, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,32 +1149,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
+          <t>https://www.indeed.com/viewjob?jk=a751147483648c6e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Application Engineer - AI</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Allspring Global Investments Holdings, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Baltimore, MD, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
+          <t>https://www.indeed.com/viewjob?jk=243ef26306c7b85a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Engineer, ML, SMAI</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boise, ID, USA USA</t>
+          <t>Las Vegas, NV, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
+          <t>https://www.indeed.com/viewjob?jk=747a30b2ad95b161</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Platform</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Omaha, NE, USA USA</t>
+          <t>Hartford, CT, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,34 +1244,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Databricks Lakehouse, SQL Server, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e10df7e2a6a34c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Cloud Services Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Detroit, MI, USA USA</t>
+          <t>KY, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ec30982bb4277ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Patterson Companies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New Orleans, LA, USA USA</t>
+          <t>CA, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,42 +1314,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d8ff32333b0bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=52f903c2e0d09915</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Cloud Services Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KY, USA USA</t>
+          <t>Anaheim, CA, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
+          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Platform Engineer - ClickHouse</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Qualys</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hartford, CT, USA USA</t>
+          <t>Foster City, CA, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,32 +1394,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,32 +1429,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc303d21d5766b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Software Engineering III - AWS, GCP, Terraform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Patterson Companies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CA, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f903c2e0d09915</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer II - Python, Databricks, ETL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Anaheim, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,34 +1489,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
+          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - ClickHouse</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Qualys</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Foster City, CA, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
+          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
         </is>
       </c>
     </row>
@@ -1564,29 +1564,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
+          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>AL, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,34 +1594,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
+          <t>https://www.indeed.com/viewjob?jk=42f767cc0538bac7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, Databricks, ETL</t>
+          <t>Sr. Software Engineer, MarTech (Remote)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,34 +1629,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
+          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Amalgamated Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,24 +1674,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
+          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Baltimore, MD, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,34 +1699,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=c7800ac2cac218cd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AL, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,24 +1744,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f767cc0538bac7</t>
+          <t>https://www.indeed.com/viewjob?jk=105c5007723a650d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LakeFusion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,34 +1769,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Kafka, Databricks Lakehouse, MongoDB, NoSQL, ELT</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71bf44c1b8f903d7</t>
+          <t>https://www.indeed.com/viewjob?jk=feed41e065eee097</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, MarTech (Remote)</t>
+          <t>Sr. AISecOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,24 +1814,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Amalgamated Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>New Orleans, LA, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,17 +1839,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
+          <t>https://www.indeed.com/viewjob?jk=18c8f5cd15d15d9f</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Detroit, MI, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1884,24 +1884,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93631fa5e9e6f5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=08f3cf35f8eeb8b0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Cyber Security Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>National Carwash Solutions, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Detroit, MI, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,42 +1909,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c769b23903df4a93</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Engineer- Software, AI and Data Analytics</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Honda Motor</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New Orleans, LA, USA USA</t>
+          <t>East Liberty, OH, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,32 +1954,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c8f5cd15d15d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. AISecOps Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,59 +1989,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
+          <t>https://www.indeed.com/viewjob?jk=4711f28285a007ae</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cyber Security Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>National Carwash Solutions, Inc.</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer- Software, AI and Data Analytics</t>
+          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Honda Motor</t>
+          <t>Vibhutechinc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>East Liberty, OH, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
+          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer - Infrastructure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>West Valley City, UT, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2093,76 +2093,6 @@
         </is>
       </c>
       <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Vibhutechinc</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Infrastructure</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>OneMain Financial</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>West Valley City, UT, USA USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=06de8d1193912d34</t>
         </is>

--- a/results/job_matches_2026-10-17.xlsx
+++ b/results/job_matches_2026-10-17.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,25 +631,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prolaio</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Arlington, TX, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Cloud Storage, Kafka</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,24 +659,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e6c438a9913e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=84b2991361adabe1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Clinical AI/Data Science Eng I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arlington, TX, USA USA</t>
+          <t>Northridge, CA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,42 +694,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b2991361adabe1</t>
+          <t>https://www.indeed.com/viewjob?jk=4af3590cefd76d17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Clinical AI/Data Science Eng I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Retail Insight Ltd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Northridge, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af3590cefd76d17</t>
+          <t>https://www.indeed.com/viewjob?jk=af18011016b66924</t>
         </is>
       </c>
     </row>
@@ -771,52 +771,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solution Architect, AI &amp; Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Advantage Investigations</t>
+          <t>Grady Health System</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NC, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
+          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Grady Health System</t>
+          <t>SEGULA Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Auburn Hills, MI, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
+          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data analyst/Data Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SEGULA Technologies</t>
+          <t>T and T Consulting Services, Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, USA USA</t>
+          <t>Falmouth, MA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,67 +869,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Senior Engineer, Agentic Engineering Governance, Open Source</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c8aaa98c8c3416fe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T and T Consulting Services, Inc</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Falmouth, MA, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,24 +939,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Engineer - AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Allspring Global Investments Holdings, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,42 +964,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2747e0e5fd2a07d7</t>
+          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Engineer, ML, SMAI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
+          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Application Engineer - AI</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Allspring Global Investments Holdings, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
+          <t>https://www.indeed.com/viewjob?jk=3095e1cfea593b51</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Engineer, ML, SMAI</t>
+          <t>Senior Cloud Services Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boise, ID, USA USA</t>
+          <t>KY, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,24 +1079,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Detroit, MI, USA USA</t>
+          <t>Hartford, CT, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ec30982bb4277ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Cloud Services Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FL, USA USA</t>
+          <t>Anaheim, CA, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,32 +1149,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a751147483648c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Platform Engineer - ClickHouse</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Qualys</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baltimore, MD, USA USA</t>
+          <t>Foster City, CA, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,32 +1184,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ef26306c7b85a</t>
+          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,102 +1219,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747a30b2ad95b161</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineering III - AWS, GCP, Terraform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hartford, CT, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Services Engineer</t>
+          <t>Software Engineer II - Python, Databricks, ETL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KY, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
+          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Patterson Companies</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CA, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f903c2e0d09915</t>
+          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Anaheim, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,34 +1349,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
+          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - ClickHouse</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Qualys</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Foster City, CA, USA USA</t>
+          <t>AL, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
+          <t>https://www.indeed.com/viewjob?jk=42f767cc0538bac7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. Software Engineer, MarTech (Remote)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,24 +1429,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
+          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,34 +1454,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
+          <t>https://www.indeed.com/viewjob?jk=feed41e065eee097</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, Databricks, ETL</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,34 +1489,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
+          <t>https://www.indeed.com/viewjob?jk=bfa5d49c34da51a2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,34 +1524,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
+          <t>https://www.indeed.com/viewjob?jk=08f3cf35f8eeb8b0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. AISecOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cyber Security Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>National Carwash Solutions, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AL, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,42 +1594,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f767cc0538bac7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, MarTech (Remote)</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,67 +1639,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
+          <t>https://www.indeed.com/viewjob?jk=4711f28285a007ae</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Engineer- Software, AI and Data Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amalgamated Bank</t>
+          <t>American Honda Motor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>East Liberty, OH, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ELT, Splunk, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
+          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Baltimore, MD, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,32 +1709,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7800ac2cac218cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vibhutechinc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,32 +1744,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105c5007723a650d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Engineer - Infrastructure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>West Valley City, UT, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1778,321 +1778,6 @@
         </is>
       </c>
       <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=feed41e065eee097</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Sr. AISecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Ally Financial</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, USA USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, USA USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18c8f5cd15d15d9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08f3cf35f8eeb8b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Cyber Security Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>National Carwash Solutions, Inc.</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Engineer- Software, AI and Data Analytics</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>American Honda Motor</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>East Liberty, OH, USA USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Vertex Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4711f28285a007ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Vibhutechinc</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Infrastructure</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>OneMain Financial</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>West Valley City, UT, USA USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=06de8d1193912d34</t>
         </is>

--- a/results/job_matches_2026-10-17.xlsx
+++ b/results/job_matches_2026-10-17.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,17 +631,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Clinical AI/Data Science Eng I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, TX, USA USA</t>
+          <t>Northridge, CA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Spark, Scala, Kafka, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,67 +659,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b2991361adabe1</t>
+          <t>https://www.indeed.com/viewjob?jk=4af3590cefd76d17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Clinical AI/Data Science Eng I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Retail Insight Ltd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Northridge, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af3590cefd76d17</t>
+          <t>https://www.indeed.com/viewjob?jk=af18011016b66924</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Retail Insight Ltd</t>
+          <t>Grady Health System</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,59 +729,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af18011016b66924</t>
+          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>SEGULA Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, USA USA</t>
+          <t>Auburn Hills, MI, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grady Health System</t>
+          <t>T and T Consulting Services, Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Falmouth, MA, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Snowflake, Oracle, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e15cf43599e45a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data analyst/Data Engineer</t>
+          <t>Senior Engineer, Agentic Engineering Governance, Open Source</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SEGULA Technologies</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
+          <t>https://www.indeed.com/viewjob?jk=c8aaa98c8c3416fe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T and T Consulting Services, Inc</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Falmouth, MA, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1a4ac9705409e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Engineer, Agentic Engineering Governance, Open Source</t>
+          <t>Application Engineer - AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Allspring Global Investments Holdings, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8aaa98c8c3416fe</t>
+          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Scala, PostgreSQL, MongoDB, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c77d94e427a3c49</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc303d21d5766b4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Application Engineer - AI</t>
+          <t>Sr Engineer, ML, SMAI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Allspring Global Investments Holdings, LLC</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,24 +974,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Engineer, ML, SMAI</t>
+          <t>Senior Cloud Services Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boise, ID, USA USA</t>
+          <t>KY, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Antonio, TX, USA USA</t>
+          <t>Hartford, CT, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,32 +1044,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3095e1cfea593b51</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Services Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KY, USA USA</t>
+          <t>Anaheim, CA, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Google Cloud Platform, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
+          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Platform Engineer - ClickHouse</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Qualys</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hartford, CT, USA USA</t>
+          <t>Foster City, CA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Anaheim, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=768f1a90f51d2256</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - ClickHouse</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qualys</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Foster City, CA, USA USA</t>
+          <t>AL, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1edf860bbbcf722d</t>
+          <t>https://www.indeed.com/viewjob?jk=42f767cc0538bac7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. Software Engineer, MarTech (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f6f4d267931c64</t>
+          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,34 +1244,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
+          <t>https://www.indeed.com/viewjob?jk=bfa5d49c34da51a2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, Databricks, ETL</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
+          <t>https://www.indeed.com/viewjob?jk=feed41e065eee097</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,34 +1314,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58094f24ce883e86</t>
+          <t>https://www.indeed.com/viewjob?jk=08f3cf35f8eeb8b0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. AISecOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,34 +1349,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90730b90dbbc0bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AL, USA USA</t>
+          <t>New Orleans, LA, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,32 +1394,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f767cc0538bac7</t>
+          <t>https://www.indeed.com/viewjob?jk=18c8f5cd15d15d9f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, MarTech (Remote)</t>
+          <t>Engineer- Software, AI and Data Analytics</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>American Honda Motor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>East Liberty, OH, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Kafka, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,32 +1429,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
+          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,32 +1464,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feed41e065eee097</t>
+          <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vibhutechinc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,32 +1499,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfa5d49c34da51a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Senior Engineer - Infrastructure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>West Valley City, UT, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1533,251 +1533,6 @@
         </is>
       </c>
       <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08f3cf35f8eeb8b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Sr. AISecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Ally Financial</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, USA USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Oracle, SQL Server, Splunk, MLOps, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f01a641164ceab7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Cyber Security Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>National Carwash Solutions, Inc.</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Vertex Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4711f28285a007ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Engineer- Software, AI and Data Analytics</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>American Honda Motor</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>East Liberty, OH, USA USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, SQL Server, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Databricks Platform Administrator – Azure &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Vibhutechinc</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4871c167266512</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Infrastructure</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>OneMain Financial</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>West Valley City, UT, USA USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=06de8d1193912d34</t>
         </is>
